--- a/القطاعات.xlsx
+++ b/القطاعات.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BEF5151-94A6-AC45-89DE-C79800224DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C86CDCF-BC0F-4ED2-A86A-CA76B47C8DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="53">
   <si>
     <t>إسكندرية</t>
   </si>
@@ -181,6 +179,18 @@
   </si>
   <si>
     <t>قبلى</t>
+  </si>
+  <si>
+    <t>المطار</t>
+  </si>
+  <si>
+    <t>التحديث المركزية</t>
+  </si>
+  <si>
+    <t>التحديث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الارشيف الالكتروني 6 اكتوبر </t>
   </si>
 </sst>
 </file>
@@ -191,14 +201,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -255,7 +265,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -557,15 +567,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="22.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.39453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -576,7 +586,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>3000</v>
       </c>
@@ -587,7 +597,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>18000</v>
       </c>
@@ -598,7 +608,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>16000</v>
       </c>
@@ -609,7 +619,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>26000</v>
       </c>
@@ -620,7 +630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3001</v>
       </c>
@@ -631,7 +641,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>17000</v>
       </c>
@@ -642,7 +652,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>17001</v>
       </c>
@@ -653,7 +663,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>18001</v>
       </c>
@@ -664,7 +674,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>18002</v>
       </c>
@@ -675,7 +685,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>5000</v>
       </c>
@@ -686,7 +696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>7000</v>
       </c>
@@ -697,7 +707,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>7001</v>
       </c>
@@ -708,7 +718,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11000</v>
       </c>
@@ -719,7 +729,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12000</v>
       </c>
@@ -730,7 +740,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13000</v>
       </c>
@@ -741,7 +751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>14000</v>
       </c>
@@ -752,7 +762,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>27000</v>
       </c>
@@ -763,7 +773,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>27003</v>
       </c>
@@ -774,7 +784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>4000</v>
       </c>
@@ -785,7 +795,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>4001</v>
       </c>
@@ -796,7 +806,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>4002</v>
       </c>
@@ -807,7 +817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>8000</v>
       </c>
@@ -818,7 +828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>10000</v>
       </c>
@@ -829,7 +839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>15000</v>
       </c>
@@ -840,7 +850,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>15001</v>
       </c>
@@ -851,7 +861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>9000</v>
       </c>
@@ -862,7 +872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>6000</v>
       </c>
@@ -873,7 +883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>6001</v>
       </c>
@@ -884,7 +894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>19000</v>
       </c>
@@ -895,7 +905,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>22002</v>
       </c>
@@ -906,7 +916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>22001</v>
       </c>
@@ -917,7 +927,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>22000</v>
       </c>
@@ -928,7 +938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>21000</v>
       </c>
@@ -939,7 +949,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>21001</v>
       </c>
@@ -950,7 +960,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>24000</v>
       </c>
@@ -961,7 +971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>24141</v>
       </c>
@@ -972,7 +982,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>20000</v>
       </c>
@@ -983,7 +993,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>20001</v>
       </c>
@@ -994,7 +1004,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>21285</v>
       </c>
@@ -1005,7 +1015,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>25000</v>
       </c>
@@ -1016,7 +1026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>23000</v>
       </c>
@@ -1027,7 +1037,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>23003</v>
       </c>
@@ -1038,7 +1048,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>9001</v>
       </c>
@@ -1049,7 +1059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>1000</v>
       </c>
@@ -1058,6 +1068,39 @@
       </c>
       <c r="C45" s="2" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>200</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>1080</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1111,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1078,7 +1121,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1087,7 +1130,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1096,7 +1139,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1105,7 +1148,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1114,7 +1157,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
